--- a/Large Market Certificates/RTS_Market_Based_Check_Jul26.xlsx
+++ b/Large Market Certificates/RTS_Market_Based_Check_Jul26.xlsx
@@ -166,7 +166,7 @@
     <t xml:space="preserve">Dashboard less market-based electricity</t>
   </si>
   <si>
-    <t xml:space="preserve">The non-electricity balance the dashboard implies (Scope 1 and anything else). Steady at ~99 t Mar-May and 70 t in Jun; 762 t in Jul</t>
+    <t xml:space="preserve">The non-electricity balance the dashboard implies (Scope 1 and anything else). Steady at ~110 t Mar-May and 86 t in Jun; 620 t in Jul</t>
   </si>
   <si>
     <t xml:space="preserve">Dashboard less location-based electricity</t>
@@ -226,7 +226,7 @@
     <t xml:space="preserve">2. Market-based electricity for RTS FELL in July, from 471.9 t (Jun) to 166.3 t, because those three accounts started crediting on 1 July. The July spike on the dashboard is not coming from the market-based electricity as it stands in the 6 Sep export.</t>
   </si>
   <si>
-    <t xml:space="preserve">3. Best fit for the 928 t: the dashboard was refreshed while the old CS Energy accounts at Maryborough (1003077, 1003082) and Torbanlea (1003571) still had no Replaced On and were accruing July (~165 + 7 + 110 = ~282 t) on top of the Engie actuals, and before the certificate accounts were linked. 739 (location-based) + 282 - 171 (HCMT deduction) + ~70-99 non-electricity = 920-950 t. The CS Energy accounts were closed at 30 Jun 26 between the 3 Sep and 5 Sep extracts, so a refresh should clear it. Scope 1 is not in this repo, so I cannot rule out a genuine July scope 1 movement - check gas and fuel for RTS if the refresh does not clear it.</t>
+    <t xml:space="preserve">3. The 8 Sep refresh brought July down from 928 t to 786 t (the CS Energy accounts at Maryborough and Torbanlea closing at 30 Jun removed their July accruals), but July is still ~230 t above June when the electricity says it should be ~300 t below. The gap (~510 t over the Mar-Jun non-electricity run-rate) is close to the two new certificate accounts not being credited at all: Auburn 204.8 t + Maryborough 196.8 t = 401.6 t, plus Torbanlea's high first Engie bill (+56 t). HCMT's deduction IS credited every month and the only structural difference is its factor - LGCs Victoria 25-26 - against the new accounts' 24-25 vintage. If the dashboard's market-based measure only picks up current-year factors, moving the accounts to 25-26 LGC factors fixes both this and item 4. Scope 1 is not in this repo, so a genuine July gas or fuel movement cannot be ruled out.</t>
   </si>
   <si>
     <t xml:space="preserve">4. All three certificate accounts are on 24-25 LGC factors (NSW -0.66, QLD -0.71) against electricity on 25-26 (0.64, 0.67), so each site nets slightly below zero: Auburn -6.2 t, Maryborough -11 t before the foundry issue. Needs the 25-26 LGC factors (already open).</t>
@@ -1421,19 +1421,19 @@
         <v>17</v>
       </c>
       <c r="B9" s="8" t="n">
-        <v>625.05</v>
+        <v>635.78</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>543.82</v>
+        <v>557.14</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>612.33</v>
+        <v>626.46</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>542.12</v>
+        <v>558.22</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>928.48</v>
+        <v>786.33</v>
       </c>
       <c r="G9" s="8"/>
       <c r="H9" s="7" t="s">
@@ -1446,23 +1446,23 @@
       </c>
       <c r="B10" s="6" t="n">
         <f aca="false">IF(B9="","",B9-B8)</f>
-        <v>98.8004999999999</v>
+        <v>109.5305</v>
       </c>
       <c r="C10" s="6" t="n">
         <f aca="false">IF(C9="","",C9-C8)</f>
-        <v>99.0203</v>
+        <v>112.3403</v>
       </c>
       <c r="D10" s="6" t="n">
         <f aca="false">IF(D9="","",D9-D8)</f>
-        <v>99.1211000000001</v>
+        <v>113.2511</v>
       </c>
       <c r="E10" s="6" t="n">
         <f aca="false">IF(E9="","",E9-E8)</f>
-        <v>70.2670999999999</v>
+        <v>86.3670999999999</v>
       </c>
       <c r="F10" s="6" t="n">
         <f aca="false">IF(F9="","",F9-F8)</f>
-        <v>762.1732</v>
+        <v>620.0232</v>
       </c>
       <c r="G10" s="6" t="str">
         <f aca="false">IF(G9="","",G9-G8)</f>
@@ -1478,23 +1478,23 @@
       </c>
       <c r="B11" s="6" t="n">
         <f aca="false">IF(B9="","",B9-B6)</f>
-        <v>-41.9319</v>
+        <v>-31.2019</v>
       </c>
       <c r="C11" s="6" t="n">
         <f aca="false">IF(C9="","",C9-C6)</f>
-        <v>-44.8430999999999</v>
+        <v>-31.5231</v>
       </c>
       <c r="D11" s="6" t="n">
         <f aca="false">IF(D9="","",D9-D6)</f>
-        <v>-60.1383</v>
+        <v>-46.0083</v>
       </c>
       <c r="E11" s="6" t="n">
         <f aca="false">IF(E9="","",E9-E6)</f>
-        <v>-92.4993000000001</v>
+        <v>-76.3993</v>
       </c>
       <c r="F11" s="6" t="n">
         <f aca="false">IF(F9="","",F9-F6)</f>
-        <v>189.4518</v>
+        <v>47.3018</v>
       </c>
       <c r="G11" s="6" t="str">
         <f aca="false">IF(G9="","",G9-G6)</f>

--- a/Large Market Certificates/RTS_Market_Based_Check_Jul26.xlsx
+++ b/Large Market Certificates/RTS_Market_Based_Check_Jul26.xlsx
@@ -104,7 +104,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1372" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1382" uniqueCount="203">
   <si>
     <t xml:space="preserve">RTS - market-based electricity check, Mar-Aug 26</t>
   </si>
@@ -157,7 +157,7 @@
     <t xml:space="preserve">What the certificates leave to report</t>
   </si>
   <si>
-    <t xml:space="preserve">Dashboard Scope 1 &amp; 2 (market-based)</t>
+    <t xml:space="preserve">Dashboard Scope 1 &amp; 2 (location-based)</t>
   </si>
   <si>
     <t xml:space="preserve">Read off the chart; blank where the chart has no bar yet</t>
@@ -166,13 +166,13 @@
     <t xml:space="preserve">Dashboard less market-based electricity</t>
   </si>
   <si>
-    <t xml:space="preserve">The non-electricity balance the dashboard implies (Scope 1 and anything else). Steady at ~110 t Mar-May and 86 t in Jun; 620 t in Jul</t>
+    <t xml:space="preserve">NOT a residual - the dashboard excludes the certificate credit, so this line double counts it. Kept only to show why it misleads</t>
   </si>
   <si>
     <t xml:space="preserve">Dashboard less location-based electricity</t>
   </si>
   <si>
-    <t xml:space="preserve">Same test with no certificate credit at all</t>
+    <t xml:space="preserve">Should equal RTS Scope 1 (Jul 47.3 vs 48.3, agrees). Negative Mar-Jun because this workbook reads the 6 Sep electricity export, which still held Torbanlea's two old CS Energy accounts - 352.8 t the 7 Sep export no longer has. See Issues</t>
   </si>
   <si>
     <t xml:space="preserve">Blue on yellow = typed in from the chart. Everything else is a formula over the Accounts tab.</t>
@@ -223,10 +223,10 @@
     <t xml:space="preserve">1. The three RTS virtual certificate accounts (Auburn x2, Maryborough QGGG000010) are calculating as set up: each mirrors its source kWh exactly in July and August, opened 1 Jul 26, no June row, and CO2e = kWh x factor. See Accounts, Check column.</t>
   </si>
   <si>
-    <t xml:space="preserve">2. Market-based electricity for RTS FELL in July, from 471.9 t (Jun) to 166.3 t, because those three accounts started crediting on 1 July. The July spike on the dashboard is not coming from the market-based electricity as it stands in the 6 Sep export.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3. The 8 Sep refresh brought July down from 928 t to 786 t (the CS Energy accounts at Maryborough and Torbanlea closing at 30 Jun removed their July accruals), but July is still ~230 t above June when the electricity says it should be ~300 t below. The gap (~510 t over the Mar-Jun non-electricity run-rate) is close to the two new certificate accounts not being credited at all: Auburn 204.8 t + Maryborough 196.8 t = 401.6 t, plus Torbanlea's high first Engie bill (+56 t). HCMT's deduction IS credited every month and the only structural difference is its factor - LGCs Victoria 25-26 - against the new accounts' 24-25 vintage. If the dashboard's market-based measure only picks up current-year factors, moving the accounts to 25-26 LGC factors fixes both this and item 4. Scope 1 is not in this repo, so a genuine July gas or fuel movement cannot be ruled out.</t>
+    <t xml:space="preserve">2. THE DASHBOARD IS LOCATION-BASED, not market-based. Scope 1 + Scope 2 with no certificate credit reproduces the chart to two decimal places (Mar 635.78, Apr 557.14, May 626.46, Jun 558.22) and to within a tonne in July. So the July rise is genuine location-based activity, not a certificate or refresh fault. Market-based electricity FELL in July, 471.9 t to 166.3 t.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. July location-based rose 104 t on June (634.6 to 739.0) on billed actuals - every RTS electricity row in July is 100% actual. Torbanlea +56.3 (first Engie bill), Auburn +19.4, Cardiff +11.9, HCMT +8.4, Maryborough +8.1. Expected RTS market-based July is 214.6 t as the data stands (Scope 1 48.3 + Scope 2 739.0 - certificates 572.7), or about 160 t once Torbanlea is credited, Maryborough follows the net figure and the certificate factors match the grid vintage.</t>
   </si>
   <si>
     <t xml:space="preserve">4. All three certificate accounts are on 24-25 LGC factors (NSW -0.66, QLD -0.71) against electricity on 25-26 (0.64, 0.67), so each site nets slightly below zero: Auburn -6.2 t, Maryborough -11 t before the foundry issue. Needs the 25-26 LGC factors (already open).</t>
@@ -238,7 +238,7 @@
     <t xml:space="preserve">6. Maryborough QGGG000320 has nothing recording since 30 Jun 26 (no Engie account yet). The interval meter reads 12,413 kWh in July and 10,262 in August, about 8 t and 7 t of uncounted location-based emissions.</t>
   </si>
   <si>
-    <t xml:space="preserve">7. Torbanlea - QTMP is a named exclusion, so no certificate account is correct. Its Engie account's first bill is 248,502 kWh for July, 51% above June's 164,454 and well above August's 170,055 - worth confirming the bill period with Engie before relying on July.</t>
+    <t xml:space="preserve">7. Torbanlea - QTMP was wrongly excluded and is now in scope: its Site Register row is green and on the Engie FY26-28 renewal, and nothing else offsets it. 900018201_3053253239_CERTS was built on 08 Sep 26. It was the largest uncredited item in RTS - 166.5 t in July, ~1,600 t/yr. Its first Engie bill is 248,502 kWh for July, 51% above June's 164,454 and above August's 170,055 - confirm the bill period with Engie before relying on July.</t>
   </si>
   <si>
     <t xml:space="preserve">8. Two meter oddities at Auburn that do not affect the account-based emissions: the NEMMCO meter on 4103713125 reads exactly twice the account every month (as Wingfield does), and sub-meter DWR_MSB-5-LATHE reads 601,436 kWh in July against 3 kWh in June - about 385 t at the NSW factor, which is almost exactly the dashboard's June-to-July increase. If the dashboard reads meters as well as accounts, that is the spike.</t>
@@ -589,13 +589,16 @@
     <t xml:space="preserve">3053253239</t>
   </si>
   <si>
-    <t xml:space="preserve">Exclude - named site (QTMP)</t>
+    <t xml:space="preserve">900018201_3053253239_CERTS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LGCs QLD 26-27</t>
   </si>
   <si>
     <t xml:space="preserve">Confirm bill</t>
   </si>
   <si>
-    <t xml:space="preserve">No certificate account is correct for a named exclusion. July's Engie bill is 248,502 kWh against 164,454 in June and 170,055 in August - confirm the bill period. Old CS Energy account 1003571 closed 30 Jun 26 in the 5 Sep extract.</t>
+    <t xml:space="preserve">Was a named exclusion until 08 Sep 26 - wrongly, its register row is green and on the Engie renewal, and nothing else offsets it. Certificate account built 08 Sep 26; it will not show in this workbook until an export taken after that. July's Engie bill is 248,502 kWh against 164,454 in June and 170,055 in August - confirm the bill period. Old CS Energy account 1003571 closed 30 Jun 26.</t>
   </si>
   <si>
     <t xml:space="preserve">ZZZZ001261</t>
@@ -646,10 +649,10 @@
     <t xml:space="preserve">Dashboard</t>
   </si>
   <si>
-    <t xml:space="preserve">July 928 t does not reconcile to the market-based electricity in the 6 Sep export (166 t). Best fit is a refresh taken while the CS Energy accounts at Maryborough and Torbanlea were still accruing July alongside the Engie actuals, before the certificate accounts were linked.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Refresh the dashboard from current data. If July stays high, pull RTS scope 1 (gas, fuel) for July - it is not in this repo.</t>
+    <t xml:space="preserve">The Scope 1 &amp; 2 chart is LOCATION-based - Scope 1 + Scope 2 with no certificate credit reproduces it to two decimal places. It is not a market-based measure and the July rise is genuine billed activity, not a data fault.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Label the measure, or add a market-based series alongside it. Expected market-based July is 214.6 t as the data stands, about 160 t once Torbanlea, Maryborough and the factor vintages are corrected.</t>
   </si>
   <si>
     <t xml:space="preserve">Open</t>
@@ -676,6 +679,15 @@
     <t xml:space="preserve">Chase the Engie account for QGGG000320 through the connector, then allocate it to Maryborough.</t>
   </si>
   <si>
+    <t xml:space="preserve">Was excluded as a named site despite a green register row on the Engie FY26-28 renewal, so 166.5 t in July carried no renewable claim. Certificate account built 08 Sep 26.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confirm with Category Management that the Engie LGC line covers NMI 3053253239, then check the next export shows the certificate mirroring its source.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In progress</t>
+  </si>
+  <si>
     <t xml:space="preserve">Engie's first bill on 900018201_3053253239 is 248,502 kWh for July, 51% above June and 46% above August.</t>
   </si>
   <si>
@@ -686,6 +698,12 @@
   </si>
   <si>
     <t xml:space="preserve">Check whether the RTS dashboard sums meters as well as accounts. Either way the sub-meter reading is a fault and should be raised with the Watt Watcher / metering provider.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">526,592 kWh / 352.8 tCO2e of Mar-Jun FY26 electricity on the two old CS Energy accounts (1003571_3053253239, 5000021_3053253239) is in the 6 Sep export and gone from the 7 Sep one. Other closed accounts still carry their history, so this is not an export rule.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Establish whether those records were deleted deliberately. If not, FY26 RTS electricity is understated by 352.8 t and needs restoring.</t>
   </si>
   <si>
     <t xml:space="preserve">NEMMCO meter 4103713125 reads twice the Origin account every month (567,561 vs 283,780 kWh in July) - the Wingfield pattern.</t>
@@ -1472,7 +1490,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
         <v>21</v>
       </c>
@@ -11905,7 +11923,7 @@
         <v>160</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>161</v>
+        <v>148</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>153</v>
@@ -11916,12 +11934,16 @@
       <c r="F6" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="G6" s="5"/>
+      <c r="G6" s="5" t="s">
+        <v>161</v>
+      </c>
       <c r="H6" s="5" t="str">
         <f aca="false">IF(G6="","n/a",IF(COUNTIFS(Accounts!$B:$B,G6)&gt;0,"Yes","No"))</f>
-        <v>n/a</v>
-      </c>
-      <c r="I6" s="5"/>
+        <v>No</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>162</v>
+      </c>
       <c r="J6" s="5" t="s">
         <v>112</v>
       </c>
@@ -11942,10 +11964,10 @@
         <v>166.4961</v>
       </c>
       <c r="O6" s="16" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P6" s="17" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11953,13 +11975,13 @@
         <v>29</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>94</v>
@@ -11993,10 +12015,10 @@
         <v>98.7423</v>
       </c>
       <c r="O7" s="16" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="P7" s="17" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12005,14 +12027,14 @@
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D8" s="5"/>
       <c r="E8" s="5" t="s">
         <v>105</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="G8" s="5" t="s">
         <v>106</v>
@@ -12044,10 +12066,10 @@
         <v>0</v>
       </c>
       <c r="O8" s="16" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="P8" s="17" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12056,14 +12078,14 @@
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D9" s="5"/>
       <c r="E9" s="5" t="s">
         <v>89</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="G9" s="5" t="s">
         <v>85</v>
@@ -12095,15 +12117,15 @@
         <v>0</v>
       </c>
       <c r="O9" s="16" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="P9" s="17" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
   </sheetData>
@@ -12153,7 +12175,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
@@ -12168,28 +12190,28 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>25</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G1" s="4" t="s">
         <v>145</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12197,20 +12219,20 @@
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D2" s="18" t="n">
-        <v>282</v>
+        <v>0</v>
       </c>
       <c r="E2" s="17" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F2" s="16"/>
       <c r="G2" s="16" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H2" s="19"/>
     </row>
@@ -12222,17 +12244,17 @@
         <v>31</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D3" s="18" t="n">
         <v>-95</v>
       </c>
       <c r="E3" s="17" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F3" s="16"/>
       <c r="G3" s="16" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H3" s="19"/>
     </row>
@@ -12241,20 +12263,20 @@
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D4" s="18" t="n">
         <v>-17</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F4" s="16"/>
       <c r="G4" s="16" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H4" s="19"/>
     </row>
@@ -12266,17 +12288,17 @@
         <v>31</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D5" s="18" t="n">
         <v>-8</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F5" s="16"/>
       <c r="G5" s="16" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H5" s="19"/>
     </row>
@@ -12288,17 +12310,17 @@
         <v>33</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D6" s="18" t="n">
-        <v>56</v>
+        <v>-166</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F6" s="16"/>
       <c r="G6" s="16" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="H6" s="19"/>
     </row>
@@ -12307,20 +12329,20 @@
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D7" s="18" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="E7" s="17" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F7" s="16"/>
       <c r="G7" s="16" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H7" s="19"/>
     </row>
@@ -12332,27 +12354,71 @@
         <v>27</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D8" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E8" s="17" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F8" s="16"/>
       <c r="G8" s="16" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H8" s="19"/>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="9" t="s">
-        <v>196</v>
+    <row r="9" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="17" t="s">
+        <v>198</v>
+      </c>
+      <c r="D9" s="18" t="n">
+        <v>-353</v>
+      </c>
+      <c r="E9" s="17" t="s">
+        <v>199</v>
+      </c>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="H9" s="19"/>
+    </row>
+    <row r="10" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="17" t="s">
+        <v>200</v>
+      </c>
+      <c r="D10" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="17" t="s">
+        <v>201</v>
+      </c>
+      <c r="F10" s="16"/>
+      <c r="G10" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="H10" s="19"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="9" t="s">
+        <v>202</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="G2:G8">
+  <conditionalFormatting sqref="G2:G10">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>"Open"</formula>
     </cfRule>
@@ -12364,7 +12430,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="G2:G8" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="G2:G10" type="list">
       <formula1>"Open,In progress,Closed,Not an issue"</formula1>
       <formula2>0</formula2>
     </dataValidation>
